--- a/csvpp_manual/CSVPP_Setup_and_Usage.xlsx
+++ b/csvpp_manual/CSVPP_Setup_and_Usage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitwork\csvpp\csvpp_manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E07B7E1-A6B6-4013-B9EB-78A2C2EA7E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A1840C-FAE3-4513-8C0E-CC4B7543E4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" activeTab="3" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
+    <workbookView xWindow="1635" yWindow="1635" windowWidth="26475" windowHeight="14280" tabRatio="858" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
   </bookViews>
   <sheets>
     <sheet name="はじめに" sheetId="28" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="313">
   <si>
     <t>内容</t>
     <rPh sb="0" eb="2">
@@ -1945,6 +1945,13 @@
     <rPh sb="22" eb="24">
       <t>ジッコウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライセンス</t>
+  </si>
+  <si>
+    <t>プログラム及び、ドキュメントは GNU General Public License version 2.0 のライセンスに従います。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3964,7 +3971,15 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>311</v>
+      </c>
       <c r="C36" s="11"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
